--- a/scenario_docs/ayo_test_scenario.xlsx
+++ b/scenario_docs/ayo_test_scenario.xlsx
@@ -4,11 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12300" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12300" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="AYO - Web" sheetId="1" r:id="rId1"/>
     <sheet name="AYO - Mobile" sheetId="3" r:id="rId2"/>
+    <sheet name="AYO - Database" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="103">
   <si>
     <t>Scenario</t>
   </si>
@@ -347,6 +348,95 @@
 4. Input nomor nomor ponsel valid '085951415092'
 5. Klik tombol 'Selanjutnya'
 6.  Berpindah ke halaman verifikasi dan menampilkan title 'Verifikasi Nomor'</t>
+  </si>
+  <si>
+    <t>Booking</t>
+  </si>
+  <si>
+    <t>User Berhasil Melakukan Booking pada Satu Venue untuk Slot 09:00 - 11:00</t>
+  </si>
+  <si>
+    <t>BOOK_001</t>
+  </si>
+  <si>
+    <t>Memastikan user dapat melakukan booking pada satu venue untuk slot waktu 09:00 - 11:00 yang tersedia.</t>
+  </si>
+  <si>
+    <t>1. Buat booking dengan user_id '1' dan venue_id '1' dengan start_time '09:00' dan end_time '11:00'
+2. Pastikan data booking terbuat</t>
+  </si>
+  <si>
+    <t>Data booking terbuat</t>
+  </si>
+  <si>
+    <t>User Berhasil Melakukan Booking pada Satu Venue untuk Dua Slot Berbeda (09:00 - 11:00 dan 13:00 - 15:00)</t>
+  </si>
+  <si>
+    <t>Memastikan user dapat melakukan beberapa booking pada venue yang sama selama slot waktu yang dipilih tidak bertabrakan.</t>
+  </si>
+  <si>
+    <t>1. Buat booking dengan user_id '1' dan venue_id '1' dengan start_time '09:00' dan end_time '11:00'
+2. 1. Buat booking dengan user_id '1' dan venue_id '1' dengan start_time '13:00' dan end_time '15:00'
+3. Pastikan data booking terbuat</t>
+  </si>
+  <si>
+    <t>User Berhasil Melakukan Booking pada Dua Venue Berbeda untuk Slot 09:00 - 11:00</t>
+  </si>
+  <si>
+    <t>BOOK_003</t>
+  </si>
+  <si>
+    <t>Memastikan user dapat melakukan booking pada beberapa venue berbeda untuk slot waktu yang sama.</t>
+  </si>
+  <si>
+    <t>1. Buat booking dengan user_id '1' dan venue_id '1' dengan start_time '09:00' dan end_time '11:00'
+2.  Buat booking dengan user_id '1' dan venue_id '2' dengan start_time '09:00' dan end_time '11:00'
+3. Pastikan data booking terbuat</t>
+  </si>
+  <si>
+    <t>User Gagal Melakukan Booking pada Venue yang Sama untuk Slot yang Sudah Dibooking (09:00 - 11:00)</t>
+  </si>
+  <si>
+    <t>BOOK_004</t>
+  </si>
+  <si>
+    <t>Memastikan sistem menolak booking duplikat pada venue dan slot waktu yang sama oleh user yang sama.</t>
+  </si>
+  <si>
+    <t>1. Buat booking dengan user_id '1' dan venue_id '1' dengan start_time '09:00' dan end_time '11:00'
+2. Buat booking dengan user_id '1' dan venue_id '1' dengan start_time '09:00' dan end_time '11:00'
+3. Pastikan data booking kedua tidak terbuat</t>
+  </si>
+  <si>
+    <t>Data booking kedua tidak terbuat</t>
+  </si>
+  <si>
+    <t>Dua User Berhasil Melakukan Booking pada Venue yang Sama dengan Slot Waktu Berbeda</t>
+  </si>
+  <si>
+    <t>BOOK_005</t>
+  </si>
+  <si>
+    <t>Memastikan beberapa user dapat melakukan booking pada venue yang sama selama menggunakan slot waktu yang berbeda.</t>
+  </si>
+  <si>
+    <t>1. Buat booking dengan user_id '1' dan venue_id '1' dengan start_time '09:00' dan end_time '11:00'
+2. Buat booking dengan user_id '2' dan venue_id '1' dengan start_time '11:00' dan end_time '13:00'
+3.  Pastikan data booking terbuat</t>
+  </si>
+  <si>
+    <t>User Kedua Gagal Melakukan Booking pada Venue dan Slot Waktu yang Sudah Dibooking oleh User Lain</t>
+  </si>
+  <si>
+    <t>BOOK_006</t>
+  </si>
+  <si>
+    <t>Memastikan sistem menolak booking pada venue dan slot waktu yang sudah dibooking oleh user lain.</t>
+  </si>
+  <si>
+    <t>1. Buat booking dengan user_id '1' dan venue_id '1' dengan start_time '09:00' dan end_time '11:00'
+2. Buat booking dengan user_id '2' dan venue_id '1' dengan start_time '09:00' dan end_time '11:00'
+3. Pastikan data booking kedua tidak terbuat</t>
   </si>
 </sst>
 </file>
@@ -976,7 +1066,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -988,6 +1078,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2107,4 +2200,229 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:J33"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="105.285714285714" customWidth="1"/>
+    <col min="3" max="3" width="12.4285714285714" customWidth="1"/>
+    <col min="4" max="4" width="31" style="1" customWidth="1"/>
+    <col min="5" max="5" width="21.7142857142857" customWidth="1"/>
+    <col min="6" max="6" width="38.8571428571429" customWidth="1"/>
+    <col min="7" max="7" width="77.8571428571429" customWidth="1"/>
+    <col min="8" max="8" width="9.85714285714286" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" ht="60" spans="1:10">
+      <c r="A2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" ht="105" spans="1:10">
+      <c r="A3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" ht="105" spans="1:10">
+      <c r="A4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" ht="120" spans="1:10">
+      <c r="A5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" ht="105" spans="1:10">
+      <c r="A6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="G6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" ht="120" spans="1:10">
+      <c r="A7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C7" t="s">
+        <v>100</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="F8" s="1"/>
+    </row>
+    <row r="19" spans="6:6">
+      <c r="F19" s="1"/>
+    </row>
+    <row r="20" spans="6:6">
+      <c r="F20" s="1"/>
+    </row>
+    <row r="21" spans="6:6">
+      <c r="F21" s="1"/>
+    </row>
+    <row r="22" spans="6:6">
+      <c r="F22" s="1"/>
+    </row>
+    <row r="28" spans="6:6">
+      <c r="F28" s="1"/>
+    </row>
+    <row r="29" spans="6:6">
+      <c r="F29" s="1"/>
+    </row>
+    <row r="30" spans="6:6">
+      <c r="F30" s="1"/>
+    </row>
+    <row r="31" spans="6:6">
+      <c r="F31" s="1"/>
+    </row>
+    <row r="32" spans="6:6">
+      <c r="F32" s="1"/>
+    </row>
+    <row r="33" spans="6:6">
+      <c r="F33" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>